--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488187_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488187_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,37 +565,37 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.024800000000001</v>
+        <v>9.356299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7897</v>
+        <v>9.757099999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7649</v>
+        <v>-0.4008</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1833</v>
+        <v>6.3658</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3835</v>
+        <v>-1.85</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7998</v>
+        <v>8.2158</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8133</v>
+        <v>8.9581</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8709</v>
+        <v>-1.4003</v>
       </c>
       <c r="L2" t="n">
-        <v>5.9423</v>
+        <v>10.3584</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.63</v>
+        <v>-2.5922</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4874</v>
+        <v>-0.4497</v>
       </c>
       <c r="O2" t="n">
         <v>-2.1426</v>
@@ -604,34 +604,34 @@
         <v>1.297</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2234</v>
+        <v>1.297</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9712</v>
+        <v>1.3785</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2711</v>
+        <v>0.5795</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5733</v>
+        <v>0.315</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.6294</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,37 +643,37 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0109</v>
+        <v>8.558299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8302</v>
+        <v>8.953799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8193</v>
+        <v>-0.3955</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3658</v>
+        <v>4.1833</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.85</v>
+        <v>0.3835</v>
       </c>
       <c r="I3" t="n">
-        <v>8.2158</v>
+        <v>3.7998</v>
       </c>
       <c r="J3" t="n">
-        <v>8.9581</v>
+        <v>6.8133</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4003</v>
+        <v>0.8709</v>
       </c>
       <c r="L3" t="n">
-        <v>10.3584</v>
+        <v>5.9423</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5922</v>
+        <v>-2.63</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4497</v>
+        <v>-0.4874</v>
       </c>
       <c r="O3" t="n">
         <v>-2.1426</v>
@@ -682,34 +682,34 @@
         <v>1.297</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.967</v>
+        <v>1.5047</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1279</v>
+        <v>0.8643</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1609</v>
+        <v>0.6404</v>
       </c>
       <c r="V3" t="n">
-        <v>0.315</v>
+        <v>1.5733</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X3" t="n">
-        <v>0.315</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.727</v>
+        <v>2.9437</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8606</v>
+        <v>1.3234</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1336</v>
+        <v>1.6203</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3754</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3567</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9814000000000001</v>
+        <v>0.8877</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7065</v>
+        <v>0.8471</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5453</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1612</v>
+        <v>0.7572</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3311</v>
+        <v>0.1393</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1885</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1426</v>
+        <v>0.1306</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>7.1849</v>
+        <v>0.8456</v>
       </c>
       <c r="T4" t="n">
-        <v>4.6932</v>
+        <v>0.4763</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4918</v>
+        <v>0.3693</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.4627</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.7766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8146</v>
+        <v>2.0914</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8423</v>
+        <v>0.1683</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9723</v>
+        <v>1.9231</v>
       </c>
       <c r="G5" t="n">
         <v>-1.3015</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8186</v>
+        <v>2.0954</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1613</v>
+        <v>1.4873</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6573</v>
+        <v>0.6081</v>
       </c>
       <c r="V5" t="n">
         <v>0.0005</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.884</v>
+        <v>0.782</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4852</v>
+        <v>3.9251</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3987</v>
+        <v>-3.1431</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.3754</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09859999999999999</v>
+        <v>1.3567</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8877</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8471</v>
+        <v>2.7065</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08989999999999999</v>
+        <v>1.5453</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7572</v>
+        <v>1.1612</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1393</v>
+        <v>-2.3311</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.1885</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1306</v>
+        <v>-2.1426</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1117</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2141</v>
+        <v>4.2398</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3619</v>
+        <v>2.7576</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1477</v>
+        <v>1.4823</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-3.4627</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3139</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.7766</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ALVAREZ GONZALEZ</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5692</v>
+        <v>0.0294</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4402</v>
+        <v>-1.4168</v>
       </c>
       <c r="F8" t="n">
-        <v>0.871</v>
+        <v>1.4462</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.082</v>
+        <v>-2.0196</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2095</v>
+        <v>-2.4971</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8725000000000001</v>
+        <v>0.4775</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2213</v>
+        <v>-1.9299</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0429</v>
+        <v>-2.1693</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2643</v>
+        <v>0.2394</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1393</v>
+        <v>-0.0897</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2524</v>
+        <v>-0.3278</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3917</v>
+        <v>0.2381</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.043</v>
+        <v>1.6604</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2189</v>
+        <v>1.1071</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1758</v>
+        <v>0.5534</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9444</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>C. ALVAREZ GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6595</v>
+        <v>-0.5199</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2419</v>
+        <v>-1.4402</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4176</v>
+        <v>0.9202</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9913</v>
+        <v>-1.082</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.311</v>
+        <v>-0.2095</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6804</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1099</v>
+        <v>-1.2213</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1514</v>
+        <v>0.0429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0415</v>
+        <v>-1.2643</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8814</v>
+        <v>0.1393</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1596</v>
+        <v>-0.2524</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7219</v>
+        <v>0.3917</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4229</v>
+        <v>0.0062</v>
       </c>
       <c r="T9" t="n">
-        <v>0.868</v>
+        <v>-0.2189</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5548</v>
+        <v>0.2251</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8174</v>
+        <v>-0.6943</v>
       </c>
       <c r="E10" t="n">
         <v>-0.7873</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0301</v>
+        <v>0.093</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6062</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2674</v>
+        <v>-0.1443</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2189</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3144</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>E. ANDRADE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0117</v>
+        <v>-0.9295</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2117</v>
+        <v>-0.8938</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>-0.0358</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0196</v>
+        <v>-4.0114</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4971</v>
+        <v>-2.1251</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4775</v>
+        <v>-1.8863</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9299</v>
+        <v>-1.7498</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1693</v>
+        <v>-1.4607</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2394</v>
+        <v>-0.2891</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0897</v>
+        <v>-2.2617</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3278</v>
+        <v>-0.6644</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2381</v>
+        <v>-1.5973</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6193</v>
+        <v>1.2498</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3121</v>
+        <v>0.5061</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3071</v>
+        <v>0.7436</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9444</v>
+        <v>2.2027</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>2.2027</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. ANDRADE</t>
+          <t>D. VIGARIO CONSTANTINO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0636</v>
+        <v>-1.1402</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0032</v>
+        <v>-0.2061</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0604</v>
+        <v>-0.9341</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.0114</v>
+        <v>-0.1091</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1251</v>
+        <v>0.152</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8863</v>
+        <v>-0.2611</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7498</v>
+        <v>0.0127</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4607</v>
+        <v>0.6656</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2891</v>
+        <v>-0.6529</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.2617</v>
+        <v>-0.1219</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6644</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5973</v>
+        <v>0.3917</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1157</v>
+        <v>-0.0137</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3967</v>
+        <v>-0.2189</v>
       </c>
       <c r="U12" t="n">
-        <v>0.719</v>
+        <v>0.2052</v>
       </c>
       <c r="V12" t="n">
-        <v>2.2027</v>
+        <v>-1.5733</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. VIGARIO CONSTANTINO</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2633</v>
+        <v>-1.1749</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2061</v>
+        <v>-0.5357</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0572</v>
+        <v>-0.6392</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1091</v>
+        <v>-1.9913</v>
       </c>
       <c r="H13" t="n">
-        <v>0.152</v>
+        <v>-1.311</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2611</v>
+        <v>-0.6804</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0127</v>
+        <v>-1.1099</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6656</v>
+        <v>-1.1514</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6529</v>
+        <v>0.0415</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1219</v>
+        <v>-0.8814</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.1596</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3917</v>
+        <v>-0.7219</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.4823</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.4823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1368</v>
+        <v>0.9075</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2189</v>
+        <v>0.5742</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.3333</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5733</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.1946</v>
+        <v>-3.3259</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.8087</v>
+        <v>-3.6446</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6141</v>
+        <v>0.3186</v>
       </c>
       <c r="G14" t="n">
         <v>-4.7562</v>
@@ -1546,13 +1546,13 @@
         <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0265</v>
+        <v>1.8952</v>
       </c>
       <c r="T14" t="n">
-        <v>0.582</v>
+        <v>0.7461</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4445</v>
+        <v>1.149</v>
       </c>
       <c r="V14" t="n">
         <v>1.5733</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>15.5041</v>
+        <v>16.5985</v>
       </c>
       <c r="E15" t="n">
-        <v>14.731</v>
+        <v>15.8253</v>
       </c>
       <c r="F15" t="n">
-        <v>0.773</v>
+        <v>0.7729000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.3443</v>
+        <v>-3.344300000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-8.719500000000002</v>
+        <v>-8.7195</v>
       </c>
       <c r="I15" t="n">
         <v>5.374899999999996</v>
@@ -1609,7 +1609,7 @@
         <v>-12.2212</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.119899999999999</v>
+        <v>-4.1199</v>
       </c>
       <c r="O15" t="n">
         <v>-8.101599999999998</v>
@@ -1624,22 +1624,22 @@
         <v>13.8965</v>
       </c>
       <c r="S15" t="n">
-        <v>14.5308</v>
+        <v>15.6251</v>
       </c>
       <c r="T15" t="n">
-        <v>7.566900000000001</v>
+        <v>8.661300000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>6.9636</v>
+        <v>6.9638</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3144999999999998</v>
+        <v>-0.3145</v>
       </c>
       <c r="W15" t="n">
         <v>7.5515</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.865899999999999</v>
+        <v>-7.8659</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.4954</v>
+        <v>9.198600000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7249</v>
+        <v>11.9207</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2295</v>
+        <v>-2.7221</v>
       </c>
       <c r="G16" t="n">
         <v>12.9515</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.1586</v>
+        <v>-2.4554</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.7509</v>
+        <v>-1.555</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4077</v>
+        <v>-0.9004</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0005</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2953</v>
+        <v>0.4237</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0045</v>
+        <v>0.4717</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2998</v>
+        <v>-0.048</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.37</v>
+        <v>2.0832</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4991</v>
+        <v>1.6882</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8691</v>
+        <v>0.395</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6118</v>
+        <v>1.6874</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7776999999999999</v>
+        <v>1.4386</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1659</v>
+        <v>0.2488</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7582</v>
+        <v>0.3958</v>
       </c>
       <c r="N17" t="n">
-        <v>1.2767</v>
+        <v>0.2496</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.035</v>
+        <v>0.1462</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-1.6595</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0396</v>
+        <v>-0.6037</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9463</v>
+        <v>-1.0558</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5733</v>
+        <v>0.3144</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0505</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2758</v>
+        <v>-1.0045</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3263</v>
+        <v>0.9379</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0832</v>
+        <v>-1.37</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6882</v>
+        <v>0.4991</v>
       </c>
       <c r="I18" t="n">
-        <v>0.395</v>
+        <v>-1.8691</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6874</v>
+        <v>-0.6118</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4386</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2488</v>
+        <v>0.1659</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3958</v>
+        <v>-0.7582</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2496</v>
+        <v>1.2767</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1462</v>
+        <v>-2.035</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1337</v>
+        <v>-0.4551</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7996</v>
+        <v>-1.0396</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3341</v>
+        <v>0.5844</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>1.5733</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5473</v>
+        <v>-0.7185</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0299</v>
+        <v>-0.2257</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5174</v>
+        <v>-0.4928</v>
       </c>
       <c r="G19" t="n">
         <v>0.068</v>
@@ -1936,13 +1936,13 @@
         <v>0.7411</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3565</v>
+        <v>-1.5277</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2014</v>
+        <v>-0.3973</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.155</v>
+        <v>-1.1304</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4718</v>
+        <v>-1.2428</v>
       </c>
       <c r="E20" t="n">
         <v>0.548</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0199</v>
+        <v>-1.7908</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4768</v>
@@ -2014,13 +2014,13 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3831</v>
+        <v>-1.154</v>
       </c>
       <c r="T20" t="n">
         <v>-0.6019</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7812</v>
+        <v>-0.5521</v>
       </c>
       <c r="V20" t="n">
         <v>1.5733</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3293</v>
+        <v>-1.6255</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3268</v>
+        <v>-3.2289</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9976</v>
+        <v>1.6034</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7274</v>
@@ -2092,13 +2092,13 @@
         <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7872</v>
+        <v>-1.0834</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0943</v>
+        <v>-0.9964</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6929</v>
+        <v>-0.0871</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.58</v>
+        <v>-3.5067</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6046</v>
+        <v>0.7025</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1846</v>
+        <v>-4.2092</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7086</v>
@@ -2170,13 +2170,13 @@
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0398</v>
+        <v>-0.9665</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2524</v>
+        <v>-0.1545</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7874</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2022</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6659</v>
+        <v>-3.6814</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0757</v>
+        <v>-2.3695</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5902</v>
+        <v>-1.3119</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7267</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1985</v>
+        <v>-1.214</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4961</v>
+        <v>-0.7899</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7024</v>
+        <v>-0.4241</v>
       </c>
       <c r="V23" t="n">
         <v>0.0005</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1311</v>
+        <v>-5.2398</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5609</v>
+        <v>-2.4629</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5702</v>
+        <v>-2.7769</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1029</v>
@@ -2326,13 +2326,13 @@
         <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2309</v>
+        <v>-1.3396</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5807</v>
+        <v>-0.4828</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6502</v>
+        <v>-0.8568</v>
       </c>
       <c r="V24" t="n">
         <v>0.3144</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.5189</v>
+        <v>-7.7394</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9287</v>
+        <v>-5.1245</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5902</v>
+        <v>-2.6148</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6459</v>
@@ -2404,13 +2404,13 @@
         <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1493</v>
+        <v>-1.3698</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1467</v>
+        <v>-0.3426</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0026</v>
+        <v>-1.0272</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9444</v>
@@ -2437,31 +2437,31 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.5041</v>
+        <v>-14.1984</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.7732000000000001</v>
+        <v>-0.7730999999999986</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.7309</v>
+        <v>-13.4252</v>
       </c>
       <c r="G26" t="n">
-        <v>3.344399999999998</v>
+        <v>3.344399999999999</v>
       </c>
       <c r="H26" t="n">
         <v>8.719399999999998</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.374699999999999</v>
+        <v>-5.374699999999998</v>
       </c>
       <c r="J26" t="n">
         <v>12.221</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1198</v>
+        <v>4.119800000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>8.1013</v>
+        <v>8.101299999999998</v>
       </c>
       <c r="M26" t="n">
         <v>-8.8765</v>
@@ -2482,13 +2482,13 @@
         <v>9.264099999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-14.5309</v>
+        <v>-13.225</v>
       </c>
       <c r="T26" t="n">
-        <v>-6.9636</v>
+        <v>-6.9637</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.5672</v>
+        <v>-6.2615</v>
       </c>
       <c r="V26" t="n">
         <v>0.3144000000000001</v>
